--- a/Libraries/Vehicle/Suspension/AxleTA4Watts/sm_car_data_Linkage_AxleTA4Watts.xlsx
+++ b/Libraries/Vehicle/Suspension/AxleTA4Watts/sm_car_data_Linkage_AxleTA4Watts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Others\smiller\ssvt_srcR22a\Libraries\Vehicle\Suspension\AxleTA4Watts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD70FA3C-45B5-4B67-A89D-B167905D24DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF99EA97-F4A6-491C-BC30-43C47CD78D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29220" yWindow="0" windowWidth="17640" windowHeight="15585" tabRatio="794" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
+    <workbookView xWindow="945" yWindow="2325" windowWidth="25485" windowHeight="11295" tabRatio="794" xr2:uid="{5368FE27-1559-47FB-BDD2-777FB297959A}"/>
   </bookViews>
   <sheets>
     <sheet name="AxleTA4Watts_SUV_Landy_r" sheetId="5" r:id="rId1"/>
@@ -313,10 +313,10 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1158,7 +1158,7 @@
       <c r="E26" s="5"/>
       <c r="F26" s="4"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="21" t="s">
+      <c r="H26" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1295,14 +1295,14 @@
       <c r="D34" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="21">
         <f>-0.2</f>
         <v>-0.2</v>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="21">
         <v>0.4</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="21">
         <v>0.9</v>
       </c>
       <c r="J34" s="14" t="s">
@@ -1323,13 +1323,13 @@
       <c r="D35" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="21">
         <v>-0.05</v>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="21">
         <v>0.6</v>
       </c>
-      <c r="H35" s="20">
+      <c r="H35" s="21">
         <v>0.3</v>
       </c>
       <c r="J35" s="14" t="s">
@@ -1382,14 +1382,14 @@
       <c r="D38" t="s">
         <v>8</v>
       </c>
-      <c r="F38" s="20">
+      <c r="F38" s="21">
         <f>2.8-2.79</f>
         <v>9.9999999999997868E-3</v>
       </c>
-      <c r="G38" s="20">
+      <c r="G38" s="21">
         <v>0.48549999999999999</v>
       </c>
-      <c r="H38" s="20">
+      <c r="H38" s="21">
         <v>0.9</v>
       </c>
       <c r="J38" s="14" t="s">
@@ -1410,14 +1410,14 @@
       <c r="D39" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="20">
+      <c r="F39" s="21">
         <f>2.8-2.79</f>
         <v>9.9999999999997868E-3</v>
       </c>
-      <c r="G39" s="20">
+      <c r="G39" s="21">
         <v>0.48549999999999999</v>
       </c>
-      <c r="H39" s="20">
+      <c r="H39" s="21">
         <v>0.54</v>
       </c>
       <c r="J39" s="14" t="s">
